--- a/resources/specs_zambia.xlsx
+++ b/resources/specs_zambia.xlsx
@@ -253,7 +253,7 @@
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
-        <t>World Bank WDI EG.ELC.ACCS.ZS, Zambia 2020 = 44.52% (World Bank/SE4ALL database). Vintage 2020. WARNING: Rural_elec_ratio and Urban_elec_ratio remain TODO — rural/urban split must share the same definition and year as this national rate before calibration can proceed. See access-definition decision note.</t>
+        <t>World Bank WDI EG.ELC.ACCS.ZS, Zambia 2020 = 44.52% (World Bank/SE4ALL database). Vintage 2020. Tested as an alternative calibration target and rejected: the rural and urban split cannot share this definition on the night-lights layer. The published calibration uses the 2023 NEAS grid-connection rates.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="2" shapeId="0">
